--- a/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-19T08:40:58+00:00</t>
+    <t>2024-09-13T08:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-13T08:09:13+00:00</t>
+    <t>2024-09-16T12:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-16T12:35:55+00:00</t>
+    <t>2024-09-18T10:20:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -642,7 +642,7 @@
 * Results from operations might involve resources that are not identified.</t>
   </si>
   <si>
-    <t>fullUrl might not be [unique in the context of a resource](bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
+    <t>fullUrl might not be [unique in the context of a resource](http://hl7.org/fhir/R4/bundle.html#bundle-unique). Note that since [FHIR resources do not need to be served through the FHIR API](http://hl7.org/fhir/R4/references.html), the fullURL might be a URN or an absolute URL that does not end with the logical id of the resource (Resource.id). However, but if the fullUrl does look like a RESTful server URL (e.g. meets the [regex](http://hl7.org/fhir/R4/references.html#regex), then the 'id' portion of the fullUrl SHALL end with the Resource.id.
 Note that the fullUrl is not the same as the canonical URL - it's an absolute url for an endpoint serving the resource (these will happen to have the same value on the canonical server for the resource with the canonical URL).</t>
   </si>
   <si>

--- a/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-18T10:20:52+00:00</t>
+    <t>2024-09-18T11:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-18T11:47:59+00:00</t>
+    <t>2024-09-23T11:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Eric-fonctionnel-desc-evenement-evaluation/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-23T11:40:21+00:00</t>
+    <t>2024-09-24T08:14:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
